--- a/data/Courses.xlsx
+++ b/data/Courses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Docencia/Cursos_asignaturas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="427" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC5BFEC2-33AC-5742-8D10-140B4ED1FF28}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E34FD9C7-E1B0-7442-8231-36A544E5B038}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$E$1:$AD$1</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -166,15 +166,6 @@
     <t>MSc in Telematic Networks and Services Engineering (MUIRST)</t>
   </si>
   <si>
-    <t>2022-Present</t>
-  </si>
-  <si>
-    <t>2021-Present</t>
-  </si>
-  <si>
-    <t>2025-Present</t>
-  </si>
-  <si>
     <t>Course Coordinator</t>
   </si>
   <si>
@@ -203,6 +194,15 @@
   </si>
   <si>
     <t>1st course</t>
+  </si>
+  <si>
+    <t>2021-Today</t>
+  </si>
+  <si>
+    <t>2022-Today</t>
+  </si>
+  <si>
+    <t>2025-Today</t>
   </si>
 </sst>
 </file>
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>31</v>
@@ -731,7 +731,7 @@
         <v>40</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>0</v>
@@ -779,19 +779,19 @@
         <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>48</v>
       </c>
       <c r="I2" s="11" t="s">
         <v>12</v>
@@ -814,19 +814,19 @@
         <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="I3" s="11" t="s">
         <v>7</v>
@@ -851,19 +851,19 @@
         <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>58</v>
-      </c>
       <c r="H4" s="11" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I4" s="11" t="s">
         <v>7</v>
@@ -886,19 +886,19 @@
         <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>16</v>
@@ -921,19 +921,19 @@
         <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>58</v>
-      </c>
       <c r="H6" s="11" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>19</v>
@@ -956,19 +956,19 @@
         <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>16</v>
@@ -991,19 +991,19 @@
         <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>16</v>
@@ -1045,16 +1045,16 @@
         <v>39</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>27</v>

--- a/data/Courses.xlsx
+++ b/data/Courses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upm365-my.sharepoint.com/personal/javier_conde_diaz_upm_es/Documents/Universidad/Docencia/Cursos_asignaturas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="434" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E34FD9C7-E1B0-7442-8231-36A544E5B038}"/>
+  <xr:revisionPtr revIDLastSave="524" documentId="11_09A831DF719B54B128E8DCE15CCE74D1AEDF1DE4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10240041-ADE6-FB4E-8636-4272D5BD633F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="2620" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$E$1:$AD$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="58">
   <si>
     <t>Año</t>
   </si>
@@ -49,24 +62,15 @@
     <t>Grado en Ingeniería de Tecnologías y Servicios de Telecomunicación (GITST)</t>
   </si>
   <si>
-    <t>47h</t>
-  </si>
-  <si>
     <t>Computación en Red (CORE)</t>
   </si>
   <si>
-    <t>189h</t>
-  </si>
-  <si>
     <t>Big Data: Fundamentos e Infraestructuras (BDFI)</t>
   </si>
   <si>
     <t>Máster Universitario en Ingeniería de Telecomunicación (MUIT)</t>
   </si>
   <si>
-    <t>42h</t>
-  </si>
-  <si>
     <t>Ingeniería de Big Data en la Nube (IBDN)</t>
   </si>
   <si>
@@ -76,30 +80,18 @@
     <t>Grado en Ingeniería y Sistemas de Datos (GISD)</t>
   </si>
   <si>
-    <t>40h</t>
-  </si>
-  <si>
     <t>Bases de Datos (BBDD)</t>
   </si>
   <si>
     <t>Grado en Ingeniería Biomédica (GIB)</t>
   </si>
   <si>
-    <t>54h</t>
-  </si>
-  <si>
     <t>Bases de Datos Relacionales y Datos Estructurados (BDRD)</t>
   </si>
   <si>
-    <t>34h</t>
-  </si>
-  <si>
     <t>Bases de Datos no Relacionales y Distribuidos (BDNR)</t>
   </si>
   <si>
-    <t>10h</t>
-  </si>
-  <si>
     <t>Sistemas de Información y Bases de Datos (SIBD)</t>
   </si>
   <si>
@@ -109,9 +101,6 @@
     <t>2021-2022</t>
   </si>
   <si>
-    <t>8h</t>
-  </si>
-  <si>
     <t>Course</t>
   </si>
   <si>
@@ -203,6 +192,24 @@
   </si>
   <si>
     <t>2025-Today</t>
+  </si>
+  <si>
+    <t>2025-26</t>
+  </si>
+  <si>
+    <t>2024-25</t>
+  </si>
+  <si>
+    <t>2023-24</t>
+  </si>
+  <si>
+    <t>2022-23</t>
+  </si>
+  <si>
+    <t>2021-22</t>
+  </si>
+  <si>
+    <t>Keep Empty</t>
   </si>
 </sst>
 </file>
@@ -261,12 +268,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -283,6 +284,11 @@
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -310,23 +316,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -342,22 +342,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -375,6 +366,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,30 +688,28 @@
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="44.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="44.83203125" customWidth="1"/>
-    <col min="5" max="7" width="85.5" style="9" customWidth="1"/>
-    <col min="8" max="8" width="36" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" style="9" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.83203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="31.5" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="18.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="26.5" style="9" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.1640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="51" style="9" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="24" style="9" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24" style="9" customWidth="1"/>
-    <col min="30" max="30" width="12.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="85.5" style="7" customWidth="1"/>
+    <col min="8" max="8" width="36" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" style="7" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.83203125" style="7" customWidth="1"/>
+    <col min="13" max="14" width="8" style="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="8" style="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="18.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="51" style="7" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="24" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24" style="7" customWidth="1"/>
+    <col min="30" max="30" width="12.5" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="9" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" s="7" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
@@ -722,528 +720,648 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+    </row>
+    <row r="2" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="21">
+        <f>SUM(L2:Q2)</f>
+        <v>42</v>
+      </c>
+      <c r="L2" s="21"/>
+      <c r="M2" s="11">
+        <v>12</v>
+      </c>
+      <c r="N2" s="11">
+        <v>12</v>
+      </c>
+      <c r="O2" s="7">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="39" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="21">
+        <f t="shared" ref="K3:K9" si="0">SUM(L3:Q3)</f>
+        <v>77</v>
+      </c>
+      <c r="L3" s="21"/>
+      <c r="M3" s="6">
         <v>30</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-    </row>
-    <row r="2" spans="1:33" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="N3" s="7">
+        <v>16</v>
+      </c>
+      <c r="O3" s="7">
+        <v>16</v>
+      </c>
+      <c r="P3" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="39" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="21">
+        <f t="shared" si="0"/>
+        <v>264</v>
+      </c>
+      <c r="L4" s="21"/>
+      <c r="M4" s="11">
+        <v>75</v>
+      </c>
+      <c r="N4" s="11">
+        <v>75</v>
+      </c>
+      <c r="O4" s="7">
+        <v>75</v>
+      </c>
+      <c r="P4" s="11">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="26" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="21">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="L5" s="21"/>
+      <c r="M5" s="11">
+        <v>19</v>
+      </c>
+      <c r="N5" s="11">
+        <v>15</v>
+      </c>
+      <c r="O5" s="7">
+        <v>15</v>
+      </c>
+      <c r="P5" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="26" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="21">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="L6" s="21"/>
+      <c r="M6" s="11">
+        <v>14</v>
+      </c>
+      <c r="N6" s="11">
+        <v>20</v>
+      </c>
+      <c r="O6" s="7">
+        <v>20</v>
+      </c>
+      <c r="P6" s="11">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="39" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="21">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L7" s="21"/>
+      <c r="M7" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" s="14" customFormat="1" ht="39" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="21">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="L8" s="22"/>
+      <c r="M8" s="20">
+        <v>10</v>
+      </c>
+      <c r="N8" s="20">
+        <v>10</v>
+      </c>
+      <c r="O8" s="6">
+        <v>10</v>
+      </c>
+      <c r="P8" s="20">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="20">
         <v>6</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="39" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+    </row>
+    <row r="9" spans="1:33" ht="39" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="12" t="s">
+      <c r="F9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="21">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="13"/>
-    </row>
-    <row r="4" spans="1:33" ht="39" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" ht="26" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="26" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" ht="39" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" s="19" customFormat="1" ht="39" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="18"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-    </row>
-    <row r="9" spans="1:33" ht="39" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>28</v>
+      <c r="L9" s="21"/>
+      <c r="Q9" s="11">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="11"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
     </row>
     <row r="12" spans="1:33" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="10"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="12"/>
-    </row>
-    <row r="13" spans="1:33" s="19" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:33" s="14" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="8"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="12"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="17"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="17"/>
-      <c r="V13" s="17"/>
-      <c r="W13" s="17"/>
-      <c r="X13" s="17"/>
-      <c r="Y13" s="17"/>
-      <c r="Z13" s="17"/>
-      <c r="AA13" s="17"/>
-      <c r="AB13" s="17"/>
-      <c r="AC13" s="17"/>
-      <c r="AD13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A14" s="10"/>
+      <c r="A14" s="8"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A15" s="10"/>
+      <c r="A15" s="8"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="12"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="11"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="9"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="12"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="8"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="11"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="9"/>
       <c r="J17" s="1"/>
-      <c r="K17" s="12"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="8"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="11"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="9"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="12"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="11"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9"/>
       <c r="J19" s="1"/>
-      <c r="K19" s="12"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="8"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="11"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="1"/>
-      <c r="K20" s="12"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="8"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="11"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9"/>
       <c r="J21" s="1"/>
-      <c r="K21" s="12"/>
-    </row>
-    <row r="22" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="H22" s="10"/>
-      <c r="K22" s="12"/>
-    </row>
-    <row r="23" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="10"/>
+      <c r="H22" s="8"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:13" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="H23" s="10"/>
-      <c r="K23" s="12"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
+      <c r="H23" s="8"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="8"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="23"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="18"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -1251,71 +1369,81 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="L25" s="23"/>
-    </row>
-    <row r="26" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
+      <c r="M25" s="18"/>
+    </row>
+    <row r="26" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="H26" s="2"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="23"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="18"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E27" s="1"/>
       <c r="H27" s="2"/>
-      <c r="L27" s="23"/>
-    </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M27" s="18"/>
+    </row>
+    <row r="28" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E28" s="1"/>
       <c r="H28" s="2"/>
-      <c r="L28" s="23"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="18"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E29" s="1"/>
       <c r="H29" s="2"/>
-      <c r="L29" s="23"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="18"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E30" s="1"/>
       <c r="H30" s="2"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="23"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="18"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E31" s="1"/>
       <c r="H31" s="2"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="23"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="18"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="E32" s="1"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="5:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E33" s="1"/>
       <c r="H33" s="2"/>
-      <c r="K33" s="12"/>
-    </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="K34" s="24"/>
-    </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="K35" s="24"/>
-    </row>
-    <row r="36" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="K36" s="12"/>
-    </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="K37" s="12"/>
-    </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="K38" s="12"/>
-    </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="K39" s="12"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.2">
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
